--- a/Instagram/PAVLOV_content_plan.xlsx
+++ b/Instagram/PAVLOV_content_plan.xlsx
@@ -2,16 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Plan" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Как пользоваться" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -29,7 +28,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
@@ -51,7 +50,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -60,22 +59,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002A2A2A"/>
+        <fgColor rgb="FF2A2A2A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6E9EE"/>
+        <fgColor rgb="FFD6E9EE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5E3D3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EDE3F2"/>
+        <fgColor rgb="FFF5E3D3"/>
       </patternFill>
     </fill>
   </fills>
@@ -89,23 +83,24 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00C8C0B4"/>
+        <color rgb="FFC8C0B4"/>
       </left>
       <right style="thin">
-        <color rgb="00C8C0B4"/>
+        <color rgb="FFC8C0B4"/>
       </right>
       <top style="thin">
-        <color rgb="00C8C0B4"/>
+        <color rgb="FFC8C0B4"/>
       </top>
       <bottom style="thin">
-        <color rgb="00C8C0B4"/>
+        <color rgb="FFC8C0B4"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -122,9 +117,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -136,7 +128,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -499,8 +491,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
@@ -554,7 +546,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="100.8" customHeight="1">
+    <row r="2" ht="151.2" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -570,24 +562,25 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Происхождение бренда. Кто это и почему вообще появилось</t>
+          <t>Кто и откуда. Происхождение бренда и диапазон в одном посте</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Свои объекты вместе: общий вид двора, терраса вечером, домик днём, сауна снаружи, крупный узел. 5–6 кадров, первый — двор целиком, чтобы было видно, что всё это одно место</t>
+          <t>Двор целиком, где домик, терраса и сауна видны вместе — это первый и главный кадр. Затем каждый объект отдельно: домик днём, терраса вечером, сауна на закате. 5–6 кадров</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
           <t>Nie znalazłem na rynku tego, czego szukałem. Więc zbudowałem sam.
-Taras z jacuzzi i kinem. Domek dla córek. Sauna. Wszystko na własnym podwórku — od pierwszego szkicu po zapalone światło.
-Jestem pierwszym klientem.</t>
+Domek dla córek. Taras z jacuzzi i kinem. Sauna. Wszystko na własnym podwórku — ten sam grafit, to samo drewno, te same obróbki.
+Tarasy i sauny to moje podwórko, nie oferta. Pokazuję je, żeby było widać, na czym stoi domek.
+Teraz projektuję domki dla innych. Jestem pierwszym klientem.</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>Последний кадр: «Zaczynam od siebie. Dosłownie.»</t>
+          <t>Последний кадр: «Wszystko, co pokazuję, stoi u mnie w ogrodzie.»</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -612,24 +605,24 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Доказательство вкуса и уровня. Главный визуал</t>
+          <t>Главный кейс. Единственный построенный домик — он работает за всё портфолио</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Терраса: все кадры одной каруселью — общий вечерний, золотой час с джакузи, интерьер с обогревателем, халат и вид в сад, ночной с экраном. 5–6 кадров, первый самый сильный</t>
+          <t>Домик: общий дневной, вид от дома, интерьер со столиком, вечерний со светом, качели снизу, лестница под конструкцией. 6 кадров, первый самый сильный</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Na rynku nie znalazłem rozwiązania, które łączyłoby jacuzzi, kino i wygodną strefę wypoczynku na 1,8 × 4,8 m. Zaprojektowałem więc własne.
-Rano kawa, w południe dzieci w wodzie, wieczorem film. Cały ogród robi się ciemny, a tutaj pali się światło.
-Nikt nigdzie nie jedzie.</t>
+          <t>Zwykle trzeba wybrać: albo tanio, albo ładnie, albo na lata. Budowałem dla córek, więc nie wybierałem.
+2 × 3,6 m. Grafit i modrzew — ten sam, co na domu. Poziome elementy zakryte obróbkami blacharskimi, schody schowane pod konstrukcją. Nic nie gnije.
+W środku firanki, półki, książki i światło.</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>Последний кадр: «Zostaje tylko usiąść.»</t>
+          <t>Последний кадр: «Domek można kupić. Własne miejsce — nie.»</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -644,33 +637,37 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>KARUZELA</t>
+          <t>REELS</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Сетка · поз. 3</t>
+          <t>Лента + сетка · поз. 3</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Второе направление. Показать, что это не единичный объект</t>
+          <t>Авторство. Первый проект, ищущий хозяина. Цена публичная</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Домик: общий дневной, от дома, интерьер со столиком, вечерний со светом, качели снизу. 5 кадров</t>
+          <t>Эскиз оживает: линии прорисовываются, разворот проекта, ключевые детали крупно. Финал — размеры и вилка цены. 15–20 сек. Единый монтаж для всех эскизов, чтобы полка читалась как полка</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Zwykle trzeba wybrać: albo tanio, albo ładnie, albo na lata. Budowałem dla córek, więc nie wybierałem.
-2 × 3,6 m. Grafit i modrzew. Poziome elementy zakryte obróbkami blacharskimi, schody schowane pod konstrukcją. Nic nie gnije.</t>
+          <t>ШАБЛОН, цифры твои. На экране:
+1) «Ten projekt szuka gospodarza»  — хук, первые 2 секунды
+2) «[Nazwa] — [wymiary]»
+3) «[Co w środku: konstrukcja, wyposażenie, światło]»
+4) «od [kwota] do [kwota]»
+5) «Zbuduję go raz — u Ciebie»</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Последний кадр: «Domek można kupić. Własne miejsce — nie.»</t>
+          <t>Финальный экран: «Napisz — dopasuję go do Twojej działki.»</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -679,7 +676,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="151.2" customHeight="1">
+    <row r="5" ht="75.59999999999999" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -690,30 +687,29 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Сетка · поз. 4 · закрепить</t>
+          <t>Сетка · поз. 4</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>КОММЕРЧЕСКОЕ ЯДРО. Единственный пост, который прямо говорит, что можно заказать сейчас</t>
+          <t>Главный дифференциатор. Показать то, чего у конкурента физически нет</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Карточки с текстом на фоне своих объектов + кадр эскиза от руки + один кадр рабочего процесса. 5–6 кадров. Верстать спокойно, без рекламной графики и без процентов скидки</t>
+          <t>Внутри домика, по кадру на позицию: шторки, полки, книжки, столик, свет, гирлянда, коврик, крючки. 8–10 кадров. Снимать при дневном свете, последний — вечерний</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Na najbliższe pół roku przyjmuję 2–3 projekty. Tyle, ile mogę poprowadzić sam — od pomysłu po ostatni detal.
-Pomysł → projekt → dopasowanie do budżetu → materiały → wykonanie → wyposażenie → gotowe miejsce.
-To pierwsze realizacje PAVLOV u klientów, więc warunki są startowe. Taki obiekt, składany przez kilka firm, kosztuje zwykle 20–25 tysięcy. U mnie teraz — 13–18.
-Nie taniej za to samo. Taniej, bo między hurtownią a Twoją działką nikt nie dolicza swojego.</t>
+          <t>Domek zwykle kupuje się pusty. Firanki, półki, światło i resztę dokupujesz sam — albo nie dokupujesz nigdy.
+U mnie domek jest gotowy w dniu montażu.
+Nic do dokupienia. Nic do dokończenia.</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Последний кадр: «Masz pomysł? Napisz — powiem, ile to kosztuje u Ciebie.»</t>
+          <t>Последний кадр: «Napisz — powiem, co wchodzi w komplet.»</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -722,82 +718,85 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="88.2" customHeight="1">
+    <row r="6" ht="75.59999999999999" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
+          <t>REELS</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Лента + сетка · поз. 5</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Второй проект. Другой размер или другой характер, чтобы был виден диапазон</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Эскиз оживает: линии прорисовываются, разворот проекта, ключевые детали крупно. Финал — размеры и вилка цены. 15–20 сек. Единый монтаж для всех эскизов, чтобы полка читалась как полка. Второй проект обязан отличаться от первого не отделкой, а замыслом: другой размер, другая крыша, другой сценарий игры</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>ШАБЛОН, цифры твои. На экране:
+1) «Ten projekt szuka gospodarza»  — хук, первые 2 секунды
+2) «[Nazwa] — [wymiary]»
+3) «[Co w środku: konstrukcja, wyposażenie, światło]»
+4) «od [kwota] do [kwota]»
+5) «Zbuduję go raz — u Ciebie»</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Финальный экран: «Napisz — powiem, czy zmieści się u Ciebie.»</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="88.2" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
           <t>KARUZELA</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Сетка · поз. 5</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Экспертиза. Показать мышление, а не объект</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Лестница: кадр снизу под домиком, крупный план узла, для контраста — как выглядит наружная лестница через пару лет (без указания на чужой объект)</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Сетка · поз. 6</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Экспертиза. Показать ход мысли, а не объект</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Лестница: кадр снизу под домиком, крупный план узла, доборники на горизонталях. Для контраста — как выглядит наружная лестница через пару лет, без указания на чужой объект. 4 кадра</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>W większości domków schody dostawia się z zewnątrz. Po kilku sezonach są do wymiany.
 Tutaj schowałem je pod konstrukcją, w suchym miejscu. Poziome elementy zakryte obróbkami blacharskimi — tak jak dach.
-Tego nie widać na zdjęciach. Widać za trzy lata.</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Последний кадр: «Tego nie widać. Widać za trzy lata.»</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="75.59999999999999" customHeight="1">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>KARUZELA</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Сетка · поз. 6</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Главный дифференциатор — полная комплектация</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Что входит: по кадру на позицию — конструкция, пол, крыша, шторы, гирлянды, обогреватель, мебель, джакузи, проектор, растения, декор. 10–12 кадров</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Konkurencja sprzedaje konstrukcję. Resztę dokupujesz sam — meble, światło, tekstylia, zieleń.
-U mnie to jeden komplet. Od pomysłu po zapalone światło.
-Nic do dokupienia. Nic do dokończenia.</t>
+Tego nie widać na zdjęciach.</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Последний кадр: «Nic do dokupienia. Nic do dokończenia.»</t>
+          <t>Последний кадр: «Planujesz domek? Napisz przed zamówieniem — powiem, na co patrzeć.»</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -806,127 +805,128 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="163.8" customHeight="1">
+    <row r="8" ht="75.59999999999999" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
+          <t>REELS</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Лента + сетка · поз. 7</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Третий проект. Замыкает ряд: видно, что проектов много и они разные</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Эскиз оживает: линии прорисовываются, разворот проекта, ключевые детали крупно. Финал — размеры и вилка цены. 15–20 сек. Единый монтаж для всех эскизов, чтобы полка читалась как полка. Третий эскиз — самый смелый: он задаёт верхнюю планку того, что можно заказать</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>ШАБЛОН, цифры твои. На экране:
+1) «Ten projekt szuka gospodarza»  — хук, первые 2 секунды
+2) «[Nazwa] — [wymiary]»
+3) «[Co w środku: konstrukcja, wyposażenie, światło]»
+4) «od [kwota] do [kwota]»
+5) «Zbuduję go raz — u Ciebie»</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Финальный экран: «Masz działkę? Napisz — pokażę, jak stanie u Ciebie.»</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="113.4" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
           <t>KARUZELA</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Сетка · поз. 7</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Аргумент цены. Почему один человек выходит дешевле цепочки — без процентов скидки</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>По кадру на роль: эскиз, каркас, доборники на горизонталях, электрика, посадка растений, мебель. Финальный кадр — готовое место целиком. 7 кадров</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Żeby powstało takie miejsce, zwykle potrzeba sześciu osób.
-Projektant narysuje. Cieśla postawi konstrukcję. Blacharz zrobi obróbki. Elektryk doprowadzi światło. Ktoś posadzi zieleń. Ktoś dobierze meble i tekstylia.
-Sześć terminów, sześć rozmów, sześć marż — i nikt nie odpowiada za całość, każdy za swój kawałek.
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Сетка · поз. 8 · закрепить</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Самый острый аргумент. Почему обычный домик портит участок, а этот — нет</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Два кадра типовых домиков — пластик, розовый, бревно. Брать из объявлений или стока, БЕЗ названий фирм. Затем свой на фоне дома: общий, и крупно совпадение графита домика с графитом дома. 5–6 кадров</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>W sklepach domki są różowe, plastikowe albo z bali. Postaw taki obok nowoczesnego domu — widać go z drugiego końca ogrodu.
+Domek dla córek ma ten sam grafit co dom i to samo drewno co taras. Stoi obok i nie rzuca się w oczy — po prostu tam jest.
+Ogród zostaje spokojny.</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Последний кадр: «Napisz — dopasuję projekt do Twojego domu.»</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="151.2" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>KARUZELA</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Сетка · поз. 9</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Объяснить цену, не называя процентов. Почему один человек выходит дешевле цепочки</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>По кадру на роль: эскиз, каркас, доборники на горизонталях, электрика, посадка зелени, обстановка внутри. Финал — готовый домик целиком. 7 кадров</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Żeby powstał taki domek, zwykle potrzeba sześciu osób. Projektant narysuje. Cieśla postawi konstrukcję. Blacharz zrobi obróbki. Elektryk doprowadzi światło. Ktoś posadzi zieleń. Ktoś dobierze tekstylia i półki.
+Sześć terminów, sześć rozmów, sześć marż — i nikt nie odpowiada za całość.
 U mnie materiały idą po cenie zakupu, z paragonami, a moja praca to kwota ustalona przed startem.
 Jeden wykonawca. Bez pośredników.</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Последний кадр: «Ile z tych sześciu masz już znalezionych?» Отвечает в комментариях — отвечаю в личку. Единственный вопрос в сетке, и он здесь не для охвата</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="88.2" customHeight="1">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>KARUZELA</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Сетка · поз. 8</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Деталь как доказательство «каждая деталь продумана»</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Кашпо: общий вид с растениями, крупно дно с туевыми ветками, схема посадки — хвойные внизу, плющ вверху</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Donice zbiłem sam. Iglaki na dole, bluszcz i barwinek wyżej, dno wyłożone gałęziami tui — woda spływa, a korzenie nie marzną.
-Zielone przez cały rok, także zimą.
-Zieleń nie jest dodatkiem: łagodzi grafitową geometrię.</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>Последний кадр: «Tego nie widać. Ale bez tego korzenie marzną.»</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="126" customHeight="1">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>KARUZELA</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Сетка · поз. 9</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Механика заказа + прямой вход. Достаточно одной картинки</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Pinterest vs реальность: скрин картинки с доски, промежуточный эскиз, фото реализации. 3–4 кадра</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Zdjęcie z Pinteresta to punkt wyjścia, nie projekt. Inny klimat, inne materiały, inne ceny.
-Adaptuję pomysł pod konkretną działkę i budżet — i dopiero wtedy powstaje coś, co da się zbudować.
-Wystarczy jeden obraz, żeby zacząć.
-Piękny pomysł szuka swojego gospodarza. Mam miejsce na dwa, może trzy, w tym półroczu.</t>
-        </is>
-      </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Последний кадр: «Wyślij swój obraz. Odpiszę, co da się z tego zrobić.»</t>
+          <t>Последний кадр: «Napisz — policzę pod Twoją działkę.»</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -941,33 +941,35 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>KARUZELA</t>
+          <t>REELS</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Сетка · позже</t>
+          <t>Лента + сетка</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Третье направление. НЕ входит в стартовые 9: фотографий бани нет ни одной, снимать</t>
+          <t>Доказать авторство. Проекты мои, а не скачанные</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Баня снаружи: 3–4 общих кадра. Внутрь не заходим, отделка не закончена</t>
+          <t>Руки, карандаш, линии на бумаге, ластик, готовый эскиз. Последний кадр — построенный домик рядом с листом. 15–20 сек, быстрая склейка</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Sauna stoi obok altany. Ten sam język: grafit na zewnątrz, drewno w środku.
-Wnętrze jeszcze w robocie — pokażę, kiedy skończę.</t>
+          <t>На экране:
+1) «Każdy domek zaczyna się tu»
+2) «Nie ma katalogu»
+3) «Jest projekt, który powstaje raz»</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Последний кадр: «Wnętrze pokażę, kiedy skończę.»</t>
+          <t>Финальный экран: «Napisz — pokażę projekty, które szukają gospodarza.»</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -976,11 +978,11 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="58" customHeight="1">
+    <row r="12" ht="63" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>REELS</t>
         </is>
@@ -992,25 +994,26 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Холодный охват. Разрыв мечты и реальности</t>
+          <t>Холодный охват. Вау от плотности: сколько влезло в 2 × 3,6</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Pinterest → эскиз → реальность. Кадр 1: картинка с доски. Кадр 2: руки, эскиз на бумаге. Кадр 3: готовый объект. 15–20 сек, быстрая склейка</t>
+          <t>Рулетка на 2 м, затем быстрая нарезка: горка, качели, гамак, песочница, лестница под конструкцией, интерьер. 15 сек, склейки в ритм</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
           <t>На экране:
-1) «Znalazłem to na Pinterest»
-2) «Adaptacja pod polską działkę»
-3) «I tak to wygląda naprawdę»</t>
+1) «2 na 3,6 metra»
+2) «Zjeżdżalnia, huśtawki, hamak, piaskownica»
+3) «Schody schowane pod spodem»
+4) «I pokój w środku»</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Финальный экран: «Wyślij swój obraz z Pinteresta. Odpiszę, jak to wygląda u Ciebie i za ile.»</t>
+          <t>Финальный экран: «Napisz — zaprojektuję pod Twój ogród i wiek dzieci.»</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1019,11 +1022,11 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="58" customHeight="1">
+    <row r="13" ht="63" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>REELS</t>
         </is>
@@ -1035,15 +1038,146 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
+          <t>Дифференциатор в движении. То, чего конкурент не покажет, потому что этого нет</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Заход внутрь домика от первого лица, панорама по деталям: шторки, полки, книжки, свет, столик. Заканчивать вечерним кадром со светом. 15–20 сек</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>На экране:
+1) «Kupujesz domek»
+2) «Dostajesz pustą skrzynię»
+3) «U mnie: firanki, półki, książki, światło»
+4) «Nic do dokupienia»</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Финальный экран: «Napisz — powiem, co wchodzi w cenę.»</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="63" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>REELS</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Лента + сетка</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Самый острый аргумент. Дизайн, который подходит дому</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Кадры типовых пластиковых и розовых домиков — сток или объявления, БЕЗ названий фирм. Затем свой на фоне дома, чтобы совпадали цвет и материал. 15 сек</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>На экране:
+1) «Twój dom»
+2) «I to, co zwykle stawia się obok»
+3) «Domek może pasować do domu»
+4) «Ten sam grafit, to samo drewno»</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Финальный экран: «Napisz — dopasuję projekt do Twojego domu.»</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>REELS</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Лента + сетка</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Экспертиза и сохраняемость. Единственный ролик, где сохранение идёт раньше контакта</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Кадр снизу под домиком, крупный план узла, доборники на горизонталях. 20 сек</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>На экране:
+1) «W większości domków schody dostawia się z zewnątrz»
+2) «Po kilku sezonach są do wymiany»
+3) «Tutaj są pod konstrukcją, w suchym miejscu»</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Финальный экран: «Zapisz, jeśli planujesz domek.» / «A jak będziesz gotów — napisz.»</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>REELS</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Лента + сетка</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
           <t>Залипательный охват. Работает без слов</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Обжиг доски: горелка, дым, огонь, щётка снимает нагар, финал — фактура крупно. 15 сек</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>На экране:
 1) «Zwykła deska»
@@ -1051,140 +1185,9 @@
 3) «Trzyma się 20 lat bez malowania»</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>Финальный экран: «Chcesz taką ścianę u siebie? Napisz — powiem, gdzie to ma sens, a gdzie nie.»</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="88.2" customHeight="1">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>REELS</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Лента + сетка</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Сохраняемость. Экспертиза в материалах. Здесь НЕ продаём — это доказательство</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Заметка о композите: рука на композитной доске в жару, термометр или просто отдёрнутая рука, рядом дерево. 20 сек</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>На экране:
-1) «Kompozyt w słońcu: 60°C»
-2) «Drewno: 35°C»
-3) «Dlatego na taras pod słońcem daję drewno»</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>Финальный экран: «Zapisz, zanim kupisz deski.» / «A jak będziesz wybierać — napisz, dobiorę pod Twoje słońce.» Единственный ролик, где сохранение идёт раньше контакта</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="63" customHeight="1">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>REELS</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Лента + сетка</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Снять страх цены. Показать абсолютную экономику, без процентов</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Смета вслух: картинка с Pinterest на экране, поверх появляются суммы. Итог диапазоном, без разбора по статьям</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>На экране:
-1) «Ile kosztuje takie miejsce?»
-2) «Przez kilka firm: 20–25 tys.»
-3) «U mnie teraz: 13–18 tys.»
-4) «Bo nikt po drodze nie dolicza swojego»</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>Финальный экран: «Wyślij zdjęcie swojej działki — policzę tak samo, na głos.»</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="63" customHeight="1">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>REELS</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Лента + сетка</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Ответ на возражение «проще съездить в отель»</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Отель vs двор: кадры отеля или спа из стока, затем своя терраса вечером. Контраст цены</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>На экране:
-1) «Weekend w hotelu SPA: 1800 zł»
-2) «Za dwoje. Dwie noce.»
-3) «Własny wieczór: raz i na zawsze»
-4) «Do hotelu trzeba pojechać. Tu wystarczy wyjść.»</t>
-        </is>
-      </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Финальный экран: «Ile razy w roku wyjeżdżasz? Napisz — policzę, ile kosztuje nie jeździć.»</t>
+          <t>Финальный экран: «Chcesz taką ścianę w domku? Napisz — powiem, gdzie to ma sens.»</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1193,41 +1196,40 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="58" customHeight="1">
+    <row r="17" ht="88.2" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>REELS</t>
+          <t>STORIS</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Лента + сетка</t>
+          <t>Кружок PROJEKTY · 1</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Процесс изменений. До/после внутри ролика</t>
+          <t>Правило полки и рамка предложения. Объяснить, как это работает, ДО того как человек начнёт выбирать</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Замена стенки или установка штор на террасе: до, процесс, после. Снимать с одной точки</t>
+          <t>Карточки текстом на фоне эскиза. Ставятся первыми в кружке и не меняются</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>На экране:
-1) «Wiatr wiał od zachodu»
-2) «Godzina roboty»
-3) «I wieczory wróciły»</t>
+          <t>Na najbliższe pół roku przyjmuję 2–3 projekty. Tyle, ile mogę poprowadzić sam — od pierwszego szkicu po ostatni detal.
+Każdy projekt powstaje raz. Wybierasz — dopasowuję do Twojej działki, potrzeb i budżetu, i buduję razem z wyposażeniem.
+Zbuduję go raz — u Ciebie.</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>Финальный экран: «Masz taras, który stoi pusty? Napisz — pokażę, co da się z nim zrobić.»</t>
+          <t>«Napisz, który projekt Cię interesuje.»</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1240,35 +1242,34 @@
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>STORIS</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Кружок OFERTA · 1</t>
+          <t>Кружок PROJEKTY · накопительный</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Ограничение. Сразу сказать, сколько проектов и на какой срок</t>
+          <t>Полка проектов. Каждый новый эскиз падает сюда — главный кружок аккаунта</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Карточка с текстом на фоне фото объекта</t>
+          <t>По карточке на эскиз: картинка, размеры, цена. Единый шаблон, чтобы полка читалась как полка</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Na najbliższe pół roku przyjmuję 2–3 projekty.
-Tyle, ile mogę poprowadzić sam — od pomysłu po ostatni detal.</t>
+          <t>Короткая подпись: название, размеры, цена. Без описаний — они в посте</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>«Kto pierwszy napisze, ten wybiera termin.»</t>
+          <t>«Ten projekt szuka gospodarza.»</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1281,35 +1282,37 @@
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>STORIS</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Кружок OFERTA · 2</t>
+          <t>Кружок PROCES</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Что именно происходит. Весь путь одной строкой</t>
+          <t>Снять страх неизвестности. Четыре шага и больше ничего</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Карточка со схемой пути</t>
+          <t>4 карточки текстом. После первого заказа переснять живьём</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Pomysł → projekt → dopasowanie do budżetu → materiały → wykonanie → wyposażenie → gotowe miejsce.
-Jedna osoba na każdym z tych kroków.</t>
+          <t>1) Wybierasz projekt — każdy ma cenę
+2) Dopasowuję go do Twojej działki, potrzeb i budżetu
+3) Ustalamy zakres i kwotę — bez zmian po drodze
+4) Buduję i urządzam. Wchodzisz do gotowego</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>«Na którym z tych kroków zwykle się zatrzymujesz?»</t>
+          <t>«Cztery kroki. Na każdym ta sama osoba.»</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1318,39 +1321,38 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="63" customHeight="1">
+    <row r="20" ht="58" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>STORIS</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Кружок OFERTA · 3</t>
+          <t>Кружок REALIZACJE</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Что беру на себя лично. Снять вопрос «а что мне придётся делать самому»</t>
+          <t>Доказательство. Только то, что построено своими руками</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Карточка со списком + фото рабочего процесса</t>
+          <t>Лучшие кадры трёх объектов: домик, терраса, сауна. Накопительный — сюда же уйдут клиентские реализации</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Biorę na siebie: rysunek i wymiary, zakup materiału, konstrukcję, obróbki blacharskie, światło, zieleń, meble i tekstylia.
-Twoje jest tylko dwoje: pomysł i budżet.</t>
+          <t>Короткие подписи по объектам: что это, размеры, из чего</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>«Reszta to mój problem, nie Twój.»</t>
+          <t>«To samo podwórko. Ten sam człowiek.»</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1359,40 +1361,40 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="88.2" customHeight="1">
+    <row r="21" ht="88.25" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>STORIS</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Кружок OFERTA · 4</t>
+          <t>Кружок O MNIE</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Почему это не сравнить с местной фирмой. Отвести сравнение с альтаной за 2 000 zł</t>
+          <t>Доверие к человеку. Происхождение бренда, ноль коммерции</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Карточка + кадр сложного узла крупно</t>
+          <t>Фото себя за работой + карточки с текстом</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>To nie jest standardowa oferta.
-Nie każdy projektant narysuje taki obiekt. Nie każdy wykonawca podejmie się nietypowych węzłów, wypalanego drewna, ukrytych schodów i elektryki naraz.
-Dlatego nie ma tego w żadnym cenniku.</t>
+          <t>Jestem pierwszym klientem.
+Chciałem, żeby córki miały swoje miejsce, a nie plastikowy zamek z marketu. Na rynku takiego nie było — więc zrobiłem sam.
+Teraz projektuję domki dla innych.</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>«Nietypowe nie znaczy droższe. Znaczy tyle, że mało kto to zrobi.»</t>
+          <t>«Zaczynam od siebie. Dlatego następne robię tak, jakby też były moje.»</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1401,338 +1403,14 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>STORIS</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Кружок OFERTA · 5</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Почему цена ниже будущей. Аргумент — ранний этап, а не неопытность</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>Карточка с текстом</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>To pierwsze realizacje PAVLOV u klientów.
-Wchodzisz wtedy, kiedy stawka jeszcze nie urosła — a robota jest ta sama, którą widzisz na tym profilu.</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>«Za rok ta sama robota będzie kosztować inaczej.»</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="63" customHeight="1">
-      <c r="A23" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>STORIS</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Кружок OFERTA · 6</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Экономика в двух числах. Клиент считает выгоду сам</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Карточка с двумя цифрами, без графиков и без процентов</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Taki obiekt, składany przez kilka firm: 20–25 tysięcy.
-U mnie teraz: 13–18 tysięcy.
-Nie taniej za to samo. Taniej, bo między hurtownią a Twoją działką nikt nie dolicza swojego.</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>«Różnicę policz sam.»</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>STORIS</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Кружок OFERTA · 7</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Дешёвый вход. Снять страх большой суммы</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Карточка + фото эскиза от руки</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>Szkic koncepcyjny — 1000 zł.
-Rysunek, główne wymiary, orientacyjny koszt realizacji.
-Jeśli robimy dalej — kwota wchodzi w cenę.</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>«Najtańszy sposób, żeby zobaczyć to na papierze.»</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>STORIS</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Кружок OFERTA · 8</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Вход в разговор. Последняя карточка кружка</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Карточка с текстом на фоне вечернего кадра</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Masz pomysł? Napisz.
-Wystarczy jedno zdjęcie i kilka zdań o miejscu.</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>«Napisz. Odpowiadam sam.» — единственная карточка кружка, которая просит</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>STORIS</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>Кружок PROCES</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>Снять страх неизвестности. Показать путь</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>4 карточки текстом, пока нет клиентов. После первого заказа переснять живьём</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>1) Piszesz i pokazujesz, co Ci się podoba
-2) Oglądam działkę, robię szkic
-3) Ustalamy zakres i kwotę — bez zmian po drodze
-4) Buduję i urządzam. Wchodzisz do gotowego</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>«Cztery kroki. Na każdym ta sama osoba.»</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="138.6" customHeight="1">
-      <c r="A27" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>STORIS</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Кружок O MNIE</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>Происхождение бренда. Здесь НЕ продаём — на это есть OFERTA</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>Фото себя за работой + карточки с текстом</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>Jestem pierwszym klientem.
-Chciałem mieć u siebie miejsce, w którym wieczorem wystarczy usiąść i nigdzie nie jechać. Na rynku takiego nie było: albo konstrukcja do samodzielnego wykończenia, albo projekt bez wykonawcy.
-Więc zrobiłem sam — taras, domek dla córek, saunę. Uczyłem się na własnym podwórku, nie na cudzym.
-Zaczynam od siebie. Dosłownie.</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>«Zaczynam od siebie. Teraz szukam kolejnych miejsc.»</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>STORIS</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Кружок ALTANY</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>Накопительный. Собирается по ходу</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>Лучшие кадры террасы из живых сторис — вечер, свет, использование</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>Короткие подписи по ходу, без сценария</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>«Wieczór, który nie wymaga przygotowań.»</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>STORIS</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Кружок DOMKI</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>Накопительный. Собирается по ходу</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>Лучшие кадры домика — дети играют, вечерний свет, детали</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>Короткие подписи по ходу, без сценария</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>«Drewno poczeka. Dzieciństwo nie.»</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
+    <row r="22" ht="58" customHeight="1"/>
+    <row r="23" ht="63" customHeight="1"/>
+    <row r="24" ht="58" customHeight="1"/>
+    <row r="25" ht="58" customHeight="1"/>
+    <row r="26" ht="58" customHeight="1"/>
+    <row r="27" ht="138.65" customHeight="1"/>
+    <row r="28" ht="58" customHeight="1"/>
+    <row r="29" ht="58" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1744,316 +1422,416 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:B37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="95" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Столбец</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Что писать</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Тип</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>REELS · KARUZELA · STORIS. Одиночных фото нет — карусель даёт больше сохранений</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Куда</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>Сетка с номером позиции / лента / конкретный кружок</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Сетка с номером позиции / лента / один из четырёх кружков</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Цель</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>Зачем эта публикация. Если цель не формулируется — публикация не нужна</t>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Зачем эта публикация. Если цель не формулируется — публикации нет. Наполнения ради наполнения в таблице не держим</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Что снимать</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Сценарий: кадры по порядку, длительность, откуда снимать</t>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Сценарий: кадры по порядку, количество, откуда снимать</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Текст</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Для карусели — подпись под постом. Для reels — текст на экране по кадрам (85% смотрят без звука)</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="7" ht="50" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Концовка</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Последний кадр карусели · финальный экран reels · последняя строка сторис. Делится не по формату, а по функции: доказательство закрывается утверждением и ничего не просит; предложение и reels просят написать и называют, что человек получит за сообщение; сторис дают повод подумать, просит только последняя карточка кружка</t>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Доказательство закрывается утверждением и ничего не просит. Эскизы и reels просят написать и называют, что человек получит за сообщение. Кружки дают повод подумать</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Статус</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>⬜ не снято · 🟡 снято, не опубликовано · ✅ опубликовано</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr"/>
-      <c r="B9" s="9" t="inlineStr"/>
+      <c r="A9" s="7" t="n"/>
+      <c r="B9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>КОММЕРЧЕСКАЯ ОСЬ</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Предложение</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>PAVLOV открывает 2–3 первых клиентских проекта на ближайшие полгода. Индивидуальный проект + полная реализация на стартовых условиях</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>Где оно живёт</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Явно — в посте №4 и в кружке OFERTA. Косвенно — в концовках reels, каждый раз другим углом. В сторис — напоминанием, сколько мест осталось</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>ЯДРО</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n"/>
+    </row>
+    <row r="11" ht="25" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Модель</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Авторская. Я придумываю проекты, клиент выбирает из моих, дальше адаптация под участок и стройка. Не подрядчик, берущий чужую идею</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="25" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Продукт</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Только детские домики. Терраса и сауна — портфолио, их никто не предлагает купить</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="25" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Эскиз</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Новая единица контента и главный источник публикаций: он не упирается в то, что построено. Пока объект один, сетку держат эскизы, а построенное работает якорем</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="25" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Пропорция</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>70–80% доказательство: объекты, детали, решения, материалы. 20–30% предложение. Не подряд — предложение просто всегда доступно</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Чего не делать</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Не называть проценты скидки. Не сравнивать с альтаной за 2 000 zł: это другой продукт. Сравнение — с ценой того же результата через цепочку</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Не «я новичок»</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Аргумент цены не «дёшево, потому что без опыта», а «вход на раннем этапе, пока ставка не выросла»</t>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Построенное перевешивает нарисованное. На старте эскизов не больше трети сетки — иначе аккаунт читается как дизайнер, который ничего не построил</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="37.5" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Цена</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>На эскизе стоит ВИЛКА, а не итог: эскиз с одними качелями и он же с двумя — разные деньги. Итоговая сумма появляется после адаптации под участок. Вилку примеряют на свой двор, она отсекает нецелевых и не превращается в обман</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Уникальность</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Каждый проект строится один раз. Обещание двустороннее: копию не получит никто, включая копию твоего</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>ПОРЯДОК ЗАПУСКА</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Любой reels попадает в сетку как обычный пост. Планка не ниже, чем для карусели</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="25" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>ЧЕТЫРЕ КРУЖКА</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>№1–9 — позиции в сетке при чтении: слева сверху направо. Публиковать в ОБРАТНОМ порядке: №9 первым, №1 последним</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>PROJEKTY</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Что можно заказать сейчас. Первая карточка — правило, дальше эскизы с ценами</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>PROCES</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Снять страх неизвестности. Четыре шага, больше ничего</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>REALIZACJE</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Доказать, что построю. Только построенное своими руками</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>O MNIE</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Доверие к человеку. Происхождение, ноль коммерции</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n"/>
+      <c r="B23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>ПОРЯДОК ЗАПУСКА</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n"/>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Предусловие</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Аккаунт не открывается, пока не готовы минимум три эскиза. Узкое место теперь не время, а количество проектов</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="25" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Нумерация</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>№1–9 — позиции в сетке при чтении, слева сверху. Публиковать в ОБРАТНОМ порядке: №9 первым, №1 последним</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Закрепить</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Позиции 1, 2 и 9: кто → что построил → что предлагает</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Ритм сетки</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Построенное → эскиз → построенное. Два эскиза подряд не ставить</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>День 1–3</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Публиковать 2–3 в день с интервалом в несколько часов. Всё сразу — посты съедают охват друг друга</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Дальше</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>2 reels + 1 карусель в неделю. Сторис через день. Ключевое — отсутствие провалов</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n"/>
+      <c r="B31" s="8" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>ВАЖНО</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>ПОРЯДОК ЗАПУСКА</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B32" s="8" t="n"/>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Reels остаётся навсегда</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>Любой reels попадает в сетку как обычный пост. Планка не ниже, чем для карусели</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>Нумерация</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>№1–9 — позиции в сетке при чтении: слева сверху направо. Публиковать в ОБРАТНОМ порядке: №9 первым, №1 последним</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>Закрепить</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Позиции 1, 2 и 4: кто → что умеет → что предлагает</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>День 1–3</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Публиковать 2–3 в день с интервалом в несколько часов. Всё сразу — посты съедают охват друг друга</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Ритм сетки</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Общий план → деталь → люди → общий. Не два похожих подряд</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>Дальше</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>2 reels + 1 карусель в неделю. Сторис через день. Ключевое — отсутствие провалов, а не количество</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="n"/>
-      <c r="B23" s="9" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Reels остаётся навсегда</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>Любой reels попадает в сетку как обычный пост. Планка не ниже, чем для карусели</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>Обложка</t>
         </is>
       </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>Для каждого reels выбрать обложку, иначе превью возьмётся из середины ролика и сломает сетку</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Для каждого reels выбрать обложку вручную, иначе превью возьмётся из середины ролика и сломает сетку</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Стикеры</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Опрос, вопрос и квиз в кружках мертвы через сутки. В постоянных кружках — только текст</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>Метрика</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>Сохранения и переходы в директ. Не лайки и не подписчики</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>Пока это правда</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>Сторис «осталось 2 места» ставить, только пока мест действительно 2</t>
         </is>

--- a/Instagram/PAVLOV_content_plan.xlsx
+++ b/Instagram/PAVLOV_content_plan.xlsx
@@ -6,8 +6,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Plan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Как пользоваться" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Лента" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Сторис" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Как пользоваться" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -491,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -557,7 +558,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Сетка · поз. 1 · закрепить</t>
+          <t>Запуск · день 1 · 📌 закрепить</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -567,7 +568,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Двор целиком, где домик, терраса и сауна видны вместе — это первый и главный кадр. Затем каждый объект отдельно: домик днём, терраса вечером, сауна на закате. 5–6 кадров</t>
+          <t>Двор целиком, где домик, терраса и сауна видны вместе — первый и главный кадр. Затем каждый объект отдельно: домик днём, терраса вечером, сауна на закате. 5–6 кадров</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -589,7 +590,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="100.8" customHeight="1">
+    <row r="3" ht="75.59999999999999" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -600,24 +601,23 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Сетка · поз. 2 · закрепить</t>
+          <t>Запуск · день 1 · 📌 закрепить</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Главный кейс. Единственный построенный домик — он работает за всё портфолио</t>
+          <t>Главный кейс. Как он сделан: конструктив, материалы, узлы</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Домик: общий дневной, вид от дома, интерьер со столиком, вечерний со светом, качели снизу, лестница под конструкцией. 6 кадров, первый самый сильный</t>
+          <t>Домик снаружи: общий дневной, вид от дома, узел крупно, доборники на горизонталях, вечерний со светом. 6 кадров. Детей и игру НЕ брать — это отдельный пост</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>Zwykle trzeba wybrać: albo tanio, albo ładnie, albo na lata. Budowałem dla córek, więc nie wybierałem.
-2 × 3,6 m. Grafit i modrzew — ten sam, co na domu. Poziome elementy zakryte obróbkami blacharskimi, schody schowane pod konstrukcją. Nic nie gnije.
-W środku firanki, półki, książki i światło.</t>
+2 × 3,6 m. Grafit i modrzew — ten sam, co na domu. Poziome elementy zakryte obróbkami blacharskimi, schody schowane pod konstrukcją. Nic nie gnije.</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -637,88 +637,88 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>KARUZELA</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Запуск · день 1</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Доказательство использования. Родитель боится не гнили, а того, что дети поиграют неделю и забудут</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Дети в домике: разное время суток, разные занятия — играют, рисуют за столиком, прячутся, вечер со светом. Снимать по ходу, накопительно. 6–8 кадров. Лица по возможности не в кадре</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>СЦЕНЫ ЗАМЕНИ НА НАСТОЯЩИЕ — я их не знаю:
+Rano zabierają tam śniadanie, po południu rysują przy stoliku, wieczorem trzeba je stamtąd wyciągać.
+Dlatego w środku są firanki, półki i światło, a nie same ściany.</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Последний кадр: «Dzieci wchodzą i zostają.»</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="63" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
           <t>REELS</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Лента + сетка · поз. 3</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Авторство. Первый проект, ищущий хозяина. Цена публичная</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Эскиз оживает: линии прорисовываются, разворот проекта, ключевые детали крупно. Финал — размеры и вилка цены. 15–20 сек. Единый монтаж для всех эскизов, чтобы полка читалась как полка</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Запуск · день 2</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Авторство. Первый проект, ищущий хозяина. Вилка цены публичная</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Эскиз оживает: линии прорисовываются, разворот проекта, ключевые детали крупно. Финал — размеры и вилка цены. 15–20 сек. Единый монтаж для всех эскизов</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>ШАБЛОН, цифры твои. На экране:
-1) «Ten projekt szuka gospodarza»  — хук, первые 2 секунды
+1) «Ten projekt szuka gospodarza» — хук, первые 2 секунды
 2) «[Nazwa] — [wymiary]»
 3) «[Co w środku: konstrukcja, wyposażenie, światło]»
 4) «od [kwota] do [kwota]»
 5) «Zbuduję go raz — u Ciebie»</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Финальный экран: «Napisz — dopasuję go do Twojej działki.»</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="75.59999999999999" customHeight="1">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>KARUZELA</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Сетка · поз. 4</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Главный дифференциатор. Показать то, чего у конкурента физически нет</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Внутри домика, по кадру на позицию: шторки, полки, книжки, столик, свет, гирлянда, коврик, крючки. 8–10 кадров. Снимать при дневном свете, последний — вечерний</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Domek zwykle kupuje się pusty. Firanki, półki, światło i resztę dokupujesz sam — albo nie dokupujesz nigdy.
-U mnie domek jest gotowy w dniu montażu.
-Nic do dokupienia. Nic do dokończenia.</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Последний кадр: «Napisz — powiem, co wchodzi w komplet.»</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="75.59999999999999" customHeight="1">
+    <row r="6" ht="88.2" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -729,32 +729,31 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Лента + сетка · поз. 5</t>
+          <t>Запуск · день 2</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Второй проект. Другой размер или другой характер, чтобы был виден диапазон</t>
+          <t>Главный дифференциатор в движении. То, чего у конкурента физически нет</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Эскиз оживает: линии прорисовываются, разворот проекта, ключевые детали крупно. Финал — размеры и вилка цены. 15–20 сек. Единый монтаж для всех эскизов, чтобы полка читалась как полка. Второй проект обязан отличаться от первого не отделкой, а замыслом: другой размер, другая крыша, другой сценарий игры</t>
+          <t>Заход внутрь домика от первого лица, панорама по деталям: шторки, полки, книжки, столик, свет. Финал — вечерний кадр со светом. 15–20 сек</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>ШАБЛОН, цифры твои. На экране:
-1) «Ten projekt szuka gospodarza»  — хук, первые 2 секунды
-2) «[Nazwa] — [wymiary]»
-3) «[Co w środku: konstrukcja, wyposażenie, światło]»
-4) «od [kwota] do [kwota]»
-5) «Zbuduję go raz — u Ciebie»</t>
+          <t>На экране:
+1) «Domek zwykle kupuje się pusty»
+2) «Firanki, półki, książki, światło»
+3) «U mnie to jeden komplet»
+4) «Nic do dokupienia»</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Финальный экран: «Napisz — powiem, czy zmieści się u Ciebie.»</t>
+          <t>Финальный экран: «Napisz — powiem, co wchodzi w komplet.»</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -763,40 +762,41 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="88.2" customHeight="1">
+    <row r="7" ht="75.59999999999999" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>KARUZELA</t>
+          <t>REELS</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Сетка · поз. 6</t>
+          <t>Запуск · день 2</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Экспертиза. Показать ход мысли, а не объект</t>
+          <t>Экспертиза и сохраняемость. Ловит человека до того, как он закажет у другого</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Лестница: кадр снизу под домиком, крупный план узла, доборники на горизонталях. Для контраста — как выглядит наружная лестница через пару лет, без указания на чужой объект. 4 кадра</t>
+          <t>Кадр снизу под домиком, крупный план узла, доборники на горизонталях. Для контраста — как выглядит наружная лестница через пару лет, без указания на чужой объект. 20 сек</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>W większości domków schody dostawia się z zewnątrz. Po kilku sezonach są do wymiany.
-Tutaj schowałem je pod konstrukcją, w suchym miejscu. Poziome elementy zakryte obróbkami blacharskimi — tak jak dach.
-Tego nie widać na zdjęciach.</t>
+          <t>На экране:
+1) «W większości domków schody dostawia się z zewnątrz»
+2) «Po kilku sezonach są do wymiany»
+3) «Tutaj są pod konstrukcją, w suchym miejscu»</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Последний кадр: «Planujesz domek? Napisz przed zamówieniem — powiem, na co patrzeć.»</t>
+          <t>Финальный экран: «Planujesz domek? Napisz przed zamówieniem — powiem, na co patrzeć.»</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="75.59999999999999" customHeight="1">
+    <row r="8" ht="63" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -816,281 +816,20 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Лента + сетка · поз. 7</t>
+          <t>Запуск · день 3 · 📌 закрепить</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Третий проект. Замыкает ряд: видно, что проектов много и они разные</t>
+          <t>Самый острый аргумент. Почему обычный домик портит участок, а этот — нет</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Эскиз оживает: линии прорисовываются, разворот проекта, ключевые детали крупно. Финал — размеры и вилка цены. 15–20 сек. Единый монтаж для всех эскизов, чтобы полка читалась как полка. Третий эскиз — самый смелый: он задаёт верхнюю планку того, что можно заказать</t>
+          <t>Два кадра типовых домиков — пластик, розовый, бревно. Из объявлений или стока, БЕЗ названий фирм. Затем свой на фоне дома, крупно совпадение графита домика с графитом дома. 15 сек</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>ШАБЛОН, цифры твои. На экране:
-1) «Ten projekt szuka gospodarza»  — хук, первые 2 секунды
-2) «[Nazwa] — [wymiary]»
-3) «[Co w środku: konstrukcja, wyposażenie, światło]»
-4) «od [kwota] do [kwota]»
-5) «Zbuduję go raz — u Ciebie»</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Финальный экран: «Masz działkę? Napisz — pokażę, jak stanie u Ciebie.»</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="113.4" customHeight="1">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>KARUZELA</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Сетка · поз. 8 · закрепить</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Самый острый аргумент. Почему обычный домик портит участок, а этот — нет</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Два кадра типовых домиков — пластик, розовый, бревно. Брать из объявлений или стока, БЕЗ названий фирм. Затем свой на фоне дома: общий, и крупно совпадение графита домика с графитом дома. 5–6 кадров</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>W sklepach domki są różowe, plastikowe albo z bali. Postaw taki obok nowoczesnego domu — widać go z drugiego końca ogrodu.
-Domek dla córek ma ten sam grafit co dom i to samo drewno co taras. Stoi obok i nie rzuca się w oczy — po prostu tam jest.
-Ogród zostaje spokojny.</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>Последний кадр: «Napisz — dopasuję projekt do Twojego domu.»</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="151.2" customHeight="1">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>KARUZELA</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Сетка · поз. 9</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Объяснить цену, не называя процентов. Почему один человек выходит дешевле цепочки</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>По кадру на роль: эскиз, каркас, доборники на горизонталях, электрика, посадка зелени, обстановка внутри. Финал — готовый домик целиком. 7 кадров</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Żeby powstał taki domek, zwykle potrzeba sześciu osób. Projektant narysuje. Cieśla postawi konstrukcję. Blacharz zrobi obróbki. Elektryk doprowadzi światło. Ktoś posadzi zieleń. Ktoś dobierze tekstylia i półki.
-Sześć terminów, sześć rozmów, sześć marż — i nikt nie odpowiada za całość.
-U mnie materiały idą po cenie zakupu, z paragonami, a moja praca to kwota ustalona przed startem.
-Jeden wykonawca. Bez pośredników.</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>Последний кадр: «Napisz — policzę pod Twoją działkę.»</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>REELS</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Лента + сетка</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Доказать авторство. Проекты мои, а не скачанные</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Руки, карандаш, линии на бумаге, ластик, готовый эскиз. Последний кадр — построенный домик рядом с листом. 15–20 сек, быстрая склейка</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>На экране:
-1) «Każdy domek zaczyna się tu»
-2) «Nie ma katalogu»
-3) «Jest projekt, który powstaje raz»</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>Финальный экран: «Napisz — pokażę projekty, które szukają gospodarza.»</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="63" customHeight="1">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>REELS</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Лента + сетка</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Холодный охват. Вау от плотности: сколько влезло в 2 × 3,6</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Рулетка на 2 м, затем быстрая нарезка: горка, качели, гамак, песочница, лестница под конструкцией, интерьер. 15 сек, склейки в ритм</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>На экране:
-1) «2 na 3,6 metra»
-2) «Zjeżdżalnia, huśtawki, hamak, piaskownica»
-3) «Schody schowane pod spodem»
-4) «I pokój w środku»</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>Финальный экран: «Napisz — zaprojektuję pod Twój ogród i wiek dzieci.»</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="63" customHeight="1">
-      <c r="A13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>REELS</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Лента + сетка</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Дифференциатор в движении. То, чего конкурент не покажет, потому что этого нет</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Заход внутрь домика от первого лица, панорама по деталям: шторки, полки, книжки, свет, столик. Заканчивать вечерним кадром со светом. 15–20 сек</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>На экране:
-1) «Kupujesz domek»
-2) «Dostajesz pustą skrzynię»
-3) «U mnie: firanki, półki, książki, światło»
-4) «Nic do dokupienia»</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>Финальный экран: «Napisz — powiem, co wchodzi w cenę.»</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="63" customHeight="1">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>REELS</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Лента + сетка</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Самый острый аргумент. Дизайн, который подходит дому</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Кадры типовых пластиковых и розовых домиков — сток или объявления, БЕЗ названий фирм. Затем свой на фоне дома, чтобы совпадали цвет и материал. 15 сек</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>На экране:
 1) «Twój dom»
@@ -1099,85 +838,263 @@
 4) «Ten sam grafit, to samo drewno»</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Финальный экран: «Napisz — dopasuję projekt do Twojego domu.»</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+    <row r="9" ht="75.59999999999999" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>REELS</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Лента + сетка</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Экспертиза и сохраняемость. Единственный ролик, где сохранение идёт раньше контакта</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Кадр снизу под домиком, крупный план узла, доборники на горизонталях. 20 сек</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Запуск · день 3</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Объяснить цену, не называя процентов. Один человек против цепочки из шести</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>По кадру на роль: эскиз, каркас, доборники, электрика, посадка зелени, обстановка внутри. Финал — готовый домик целиком. 20 сек</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>На экране:
-1) «W większości domków schody dostawia się z zewnątrz»
-2) «Po kilku sezonach są do wymiany»
-3) «Tutaj są pod konstrukcją, w suchym miejscu»</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>Финальный экран: «Zapisz, jeśli planujesz domek.» / «A jak będziesz gotów — napisz.»</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
+1) «Żeby powstał taki domek, potrzeba sześciu osób»
+2) «Projektant, cieśla, blacharz, elektryk, ogrodnik, dekorator»
+3) «Sześć terminów, sześć marż»
+4) «Jeden wykonawca. Bez pośredników»</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Финальный экран: «Napisz — policzę pod Twoją działkę.»</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>REELS</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Лента + сетка</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Запуск · день 3</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Второй проект. Другой размер и другой замысел, а не другая отделка</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Эскиз оживает: линии прорисовываются, разворот проекта, ключевые детали крупно. Финал — размеры и вилка цены. 15–20 сек. Единый монтаж для всех эскизов. Второй проект обязан отличаться от первого замыслом: другой размер, другая крыша, другой сценарий игры</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>ШАБЛОН, цифры твои. На экране:
+1) «Ten projekt szuka gospodarza» — хук, первые 2 секунды
+2) «[Nazwa] — [wymiary]»
+3) «[Co w środku: konstrukcja, wyposażenie, światło]»
+4) «od [kwota] do [kwota]»
+5) «Zbuduję go raz — u Ciebie»</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Финальный экран: «Napisz — powiem, czy zmieści się u Ciebie.»</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="75.59999999999999" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>REELS</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Дальше · ритм</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Третий проект. Задаёт верхнюю планку того, что можно заказать</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Эскиз оживает: линии прорисовываются, разворот проекта, ключевые детали крупно. Финал — размеры и вилка цены. 15–20 сек. Единый монтаж для всех эскизов. Третий эскиз — самый смелый из трёх</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>ШАБЛОН, цифры твои. На экране:
+1) «Ten projekt szuka gospodarza» — хук, первые 2 секунды
+2) «[Nazwa] — [wymiary]»
+3) «[Co w środku: konstrukcja, wyposażenie, światło]»
+4) «od [kwota] do [kwota]»
+5) «Zbuduję go raz — u Ciebie»</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Финальный экран: «Masz działkę? Napisz — pokażę, jak stanie u Ciebie.»</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="63" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>REELS</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Дальше · ритм</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Холодный охват. Вау от плотности: сколько функций влезло в 2 × 3,6</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Рулетка на 2 м, затем быстрая нарезка: горка, качели, гамак, песочница, лестница под конструкцией, комната внутри. 15 сек, склейки в ритм</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>На экране:
+1) «2 na 3,6 metra»
+2) «Zjeżdżalnia, huśtawki, hamak, piaskownica»
+3) «I pokój w środku»
+4) «Wszystko naraz»</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Финальный экран: «Napisz — zaprojektuję pod Twój ogród i wiek dzieci.»</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>REELS</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Дальше · ритм</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Доказать авторство. Проекты мои, а не скачанные</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Руки, карандаш, линии на бумаге, ластик, готовый эскиз. Последний кадр — построенный домик рядом с листом. 15–20 сек</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>На экране:
+1) «Każdy domek zaczyna się tu»
+2) «Nie ma katalogu»
+3) «Jest projekt, który powstaje raz»</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Финальный экран: «Napisz — pokażę projekty, które szukają gospodarza.»</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>REELS</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Дальше · ритм</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Залипательный охват. Работает без слов</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Обжиг доски: горелка, дым, огонь, щётка снимает нагар, финал — фактура крупно. 15 сек</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>На экране:
 1) «Zwykła deska»
@@ -1185,232 +1102,31 @@
 3) «Trzyma się 20 lat bez malowania»</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>Финальный экран: «Chcesz taką ścianę w domku? Napisz — powiem, gdzie to ma sens.»</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="88.2" customHeight="1">
-      <c r="A17" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>STORIS</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Кружок PROJEKTY · 1</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Правило полки и рамка предложения. Объяснить, как это работает, ДО того как человек начнёт выбирать</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Карточки текстом на фоне эскиза. Ставятся первыми в кружке и не меняются</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Na najbliższe pół roku przyjmuję 2–3 projekty. Tyle, ile mogę poprowadzić sam — od pierwszego szkicu po ostatni detal.
-Każdy projekt powstaje raz. Wybierasz — dopasowuję do Twojej działki, potrzeb i budżetu, i buduję razem z wyposażeniem.
-Zbuduję go raz — u Ciebie.</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>«Napisz, który projekt Cię interesuje.»</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>STORIS</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Кружок PROJEKTY · накопительный</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Полка проектов. Каждый новый эскиз падает сюда — главный кружок аккаунта</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>По карточке на эскиз: картинка, размеры, цена. Единый шаблон, чтобы полка читалась как полка</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Короткая подпись: название, размеры, цена. Без описаний — они в посте</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>«Ten projekt szuka gospodarza.»</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>STORIS</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Кружок PROCES</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Снять страх неизвестности. Четыре шага и больше ничего</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>4 карточки текстом. После первого заказа переснять живьём</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>1) Wybierasz projekt — każdy ma cenę
-2) Dopasowuję go do Twojej działki, potrzeb i budżetu
-3) Ustalamy zakres i kwotę — bez zmian po drodze
-4) Buduję i urządzam. Wchodzisz do gotowego</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>«Cztery kroki. Na każdym ta sama osoba.»</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>STORIS</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Кружок REALIZACJE</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Доказательство. Только то, что построено своими руками</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Лучшие кадры трёх объектов: домик, терраса, сауна. Накопительный — сюда же уйдут клиентские реализации</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Короткие подписи по объектам: что это, размеры, из чего</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>«To samo podwórko. Ten sam człowiek.»</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="88.25" customHeight="1">
-      <c r="A21" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>STORIS</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Кружок O MNIE</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Доверие к человеку. Происхождение бренда, ноль коммерции</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Фото себя за работой + карточки с текстом</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>Jestem pierwszym klientem.
-Chciałem, żeby córki miały swoje miejsce, a nie plastikowy zamek z marketu. Na rynku takiego nie było — więc zrobiłem sam.
-Teraz projektuję domki dla innych.</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>«Zaczynam od siebie. Dlatego następne robię tak, jakby też były moje.»</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1"/>
-    <row r="23" ht="63" customHeight="1"/>
+    <row r="15" ht="58" customHeight="1"/>
+    <row r="16" ht="88.25" customHeight="1"/>
+    <row r="17" ht="58" customHeight="1"/>
+    <row r="18" ht="58" customHeight="1"/>
+    <row r="19" ht="58" customHeight="1"/>
+    <row r="20" ht="88.25" customHeight="1"/>
+    <row r="21" ht="58" customHeight="1"/>
+    <row r="22" ht="63" customHeight="1"/>
+    <row r="23" ht="58" customHeight="1"/>
     <row r="24" ht="58" customHeight="1"/>
     <row r="25" ht="58" customHeight="1"/>
-    <row r="26" ht="58" customHeight="1"/>
-    <row r="27" ht="138.65" customHeight="1"/>
+    <row r="26" ht="138.65" customHeight="1"/>
+    <row r="27" ht="58" customHeight="1"/>
     <row r="28" ht="58" customHeight="1"/>
-    <row r="29" ht="58" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1422,7 +1138,286 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Кружок</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Цель</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Что снимать</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Текст карточек</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Концовка</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="214.2" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>OFERTA</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Инструкция предложения. Что можно заказать и как это работает</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>4 карточки текстом на фоне эскизов и своих объектов. Ставятся один раз и дальше не меняются</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>1) Na najbliższe pół roku przyjmuję 2–3 projekty. Tyle, ile mogę poprowadzić sam.
+   Każdy projekt powstaje raz — zbuduję go u Ciebie i nie powtórzę u nikogo.
+2) Jak to działa: wybierasz projekt → dopasowuję do Twojej działki, potrzeb i budżetu →
+   ustalamy zakres i kwotę, bez zmian po drodze → buduję i urządzam.
+3) Co wchodzi w cenę: materiały po cenie zakupu z paragonami · konstrukcja i obróbki ·
+   światło · firanki, półki, tekstylia · montaż.
+   Moja praca to kwota ustalona przed startem.
+4) Masz działkę i dzieci? Napisz — powiem, który projekt się zmieści.</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>«Napisz. Odpowiadam sam.»</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="58" customHeight="1">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>PROJEKTY</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Полка проектов. Только эскизы, ничего кроме</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>По карточке на эскиз: картинка, размеры, вилка цены. Единый шаблон, чтобы полка читалась полкой. Накопительный — каждый новый эскиз падает сюда</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Короткая подпись: название, размеры, вилка. Описания живут в посте, здесь только выбор</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>«Ten projekt szuka gospodarza.»</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="58" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>PROCES</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Как я строю. Снять страх «а как это будет выглядеть по ходу»</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Этапы стройки из того, что есть. На старте хватит пары сторис, наполнится на первой клиентской стройке</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Короткие подписи по этапам: что делается и зачем</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>«Buduję sam. Zobaczysz każdy etap.»</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>REALIZACJE</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Клиентские объекты. ПУСТ до первой реализации — заводить, когда появится первая</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Короткая одностраничная версия каждой реализации: один-два кадра готового объекта у клиента. Полная версия идёт роликом в ленту, сюда — выжимка</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Где, какой проект был исходным, что адаптировали под участок</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>«Ten projekt ma już gospodarza.»</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="75.59999999999999" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>O MNIE</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Доверие к человеку. Происхождение бренда, ноль коммерции</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Фото себя за работой + карточки с текстом</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Jestem pierwszym klientem.
+Chciałem, żeby córki miały swoje miejsce, a nie plastikowy zamek z marketu. Na rynku takiego nie było — więc zrobiłem sam.
+Teraz projektuję domki dla innych.</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>«Zaczynam od siebie. Dosłownie.»</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>— живые сторис, вне кружков —</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Удержание и корм для кружков. Из десяти одна попадает в кружок, девять живут сутки</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Работа, поездка за материалом, стройка, вечер во дворе. **Личное остаётся здесь и только на сутки** — в кружки не сохраняется</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Регулярные форматы: новый эскиз ищет хозяина · сколько мест осталось, пока это правда · наблюдение из работы</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Стикеры работают только здесь. В кружках они мертвы через сутки</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1430,38 +1425,38 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>Столбец</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>Что писать</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Лист</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Что в нём</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Тип</t>
+          <t>Лента</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>REELS · KARUZELA · STORIS. Одиночных фото нет — карусель даёт больше сохранений</t>
+          <t>Карусели и рилсы. Сначала девять позиций запуска, ниже — то, что идёт дальше по ритму</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Куда</t>
+          <t>Сторис</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>Сетка с номером позиции / лента / один из четырёх кружков</t>
+          <t>Кружки и живые сторис. Один кружок — одна строка, карточки внутри ячейки</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1475,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Что снимать</t>
+          <t>КОЛОНКИ</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -1492,50 +1487,62 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Текст</t>
+          <t>Цель</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Для карусели — подпись под постом. Для reels — текст на экране по кадрам (85% смотрят без звука)</t>
+          <t>Зачем эта публикация. Если цель не формулируется — публикации нет</t>
         </is>
       </c>
     </row>
     <row r="7" ht="50" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Концовка</t>
+          <t>Что снимать</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Доказательство закрывается утверждением и ничего не просит. Эскизы и reels просят написать и называют, что человек получит за сообщение. Кружки дают повод подумать</t>
+          <t>Кадры по порядку, количество, откуда снимать</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Статус</t>
+          <t>Текст</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>⬜ не снято · 🟡 снято, не опубликовано · ✅ опубликовано</t>
+          <t>Для карусели — подпись под постом. Для рилса — текст на экране по кадрам, 85% смотрят без звука</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="8" t="n"/>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Концовка</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Каждая ведёт к контакту и называет, что человек получит за сообщение. Исключение — пост о происхождении: там концовка закрывает историю</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>ЯДРО</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n"/>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>⬜ не снято · 🟡 снято, не опубликовано · ✅ опубликовано</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="25" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
@@ -1552,7 +1559,7 @@
     <row r="12" ht="25" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Продукт</t>
+          <t>ЯДРО</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
@@ -1564,72 +1571,72 @@
     <row r="13" ht="25" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Эскиз</t>
+          <t>Модель</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Новая единица контента и главный источник публикаций: он не упирается в то, что построено. Пока объект один, сетку держат эскизы, а построенное работает якорем</t>
+          <t>Авторская. Проекты мои, клиент выбирает из моих, дальше адаптация под участок и стройка</t>
         </is>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Пропорция</t>
+          <t>Продукт</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Построенное перевешивает нарисованное. На старте эскизов не больше трети сетки — иначе аккаунт читается как дизайнер, который ничего не построил</t>
+          <t>Только детские домики. Терраса и сауна — своё подворье, не оферта</t>
         </is>
       </c>
     </row>
     <row r="15" ht="37.5" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Цена</t>
+          <t>Эскиз</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>На эскизе стоит ВИЛКА, а не итог: эскиз с одними качелями и он же с двумя — разные деньги. Итоговая сумма появляется после адаптации под участок. Вилку примеряют на свой двор, она отсекает нецелевых и не превращается в обман</t>
+          <t>Главный источник публикаций: не упирается в то, что построено. Пока объект один, ленту держат эскизы</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Уникальность</t>
+          <t>Цена</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Каждый проект строится один раз. Обещание двустороннее: копию не получит никто, включая копию твоего</t>
+          <t>На эскизе стоит ВИЛКА, не итог: проект с одними качелями и он же с двумя — разные деньги. Итог появляется после адаптации</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>ПОРЯДОК ЗАПУСКА</t>
+          <t>Уникальность</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Любой reels попадает в сетку как обычный пост. Планка не ниже, чем для карусели</t>
+          <t>Каждый проект строится один раз. Копию не получит никто, включая копию твоего</t>
         </is>
       </c>
     </row>
     <row r="18" ht="25" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>ЧЕТЫРЕ КРУЖКА</t>
+          <t>Пропорция</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>№1–9 — позиции в сетке при чтении: слева сверху направо. Публиковать в ОБРАТНОМ порядке: №9 первым, №1 последним</t>
+          <t>Рилсов больше, чем каруселей, и это правильно на старте: рилс — единственный холодный вход, карусель работает на тех, кто уже пришёл</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1655,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>PROCES</t>
+          <t>ЗАПУСК</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -1660,48 +1667,60 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>REALIZACJE</t>
+          <t>Предусловие</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Доказать, что построю. Только построенное своими руками</t>
+          <t>Не открывать, пока нет минимум двух эскизов. Узкое место не время, а количество проектов</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>O MNIE</t>
+          <t>Закрепить</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Доверие к человеку. Происхождение, ноль коммерции</t>
+          <t>Три поста уходят наверх сетки и стоят там всегда: двор, домик и дизайн — кто, что построил, чем отличаюсь. Помечены 📌 в колонке «Куда»</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="n"/>
-      <c r="B23" s="8" t="n"/>
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Ритм сетки</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Позиции в сетке не нумеруются: они живут до десятого поста, дальше всё сползает вниз. Постоянны только три закреплённых. Единственное правило очереди — два эскиза подряд не ставить</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>ПОРЯДОК ЗАПУСКА</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="n"/>
+          <t>День 1–3</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>День 1 — три карусели, чтобы в профиле было что смотреть. Дни 2 и 3 — рилсы: рилс гонит трафик в профиль, и профиль к этому моменту не должен быть пустым</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>Предусловие</t>
+          <t>Дальше</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Аккаунт не открывается, пока не готовы минимум три эскиза. Узкое место теперь не время, а количество проектов</t>
+          <t>2 рилса + 1 карусель в неделю. Сторис через день. Ключевое — отсутствие провалов</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1739,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Закрепить</t>
+          <t>ВАЖНО</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -1732,111 +1751,52 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Ритм сетки</t>
+          <t>Рилс остаётся навсегда</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Построенное → эскиз → построенное. Два эскиза подряд не ставить</t>
+          <t>Любой рилс попадает в сетку как обычный пост. Планка не ниже, чем для карусели</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>День 1–3</t>
+          <t>Обложка</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Публиковать 2–3 в день с интервалом в несколько часов. Всё сразу — посты съедают охват друг друга</t>
+          <t>Для каждого рилса выбрать вручную, иначе превью возьмётся из середины и сломает сетку</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Дальше</t>
+          <t>Метрика</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>2 reels + 1 карусель в неделю. Сторис через день. Ключевое — отсутствие провалов</t>
+          <t>Сохранения и переходы в директ. Не лайки и не подписчики</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="n"/>
-      <c r="B31" s="8" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="n"/>
-    </row>
-    <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>Reels остаётся навсегда</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Любой reels попадает в сетку как обычный пост. Планка не ниже, чем для карусели</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>Обложка</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>Для каждого reels выбрать обложку вручную, иначе превью возьмётся из середины ролика и сломает сетку</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>Стикеры</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>Опрос, вопрос и квиз в кружках мертвы через сутки. В постоянных кружках — только текст</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>Метрика</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>Сохранения и переходы в директ. Не лайки и не подписчики</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>Пока это правда</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>Сторис «осталось 2 места» ставить, только пока мест действительно 2</t>
-        </is>
-      </c>
-    </row>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>«Осталось 2 места» ставить, только пока мест действительно 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Instagram/PAVLOV_content_plan.xlsx
+++ b/Instagram/PAVLOV_content_plan.xlsx
@@ -573,10 +573,10 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>Nie znalazłem na rynku tego, czego szukałem. Więc zbudowałem sam.
-Domek dla córek. Taras z jacuzzi i kinem. Sauna. Wszystko na własnym podwórku — ten sam grafit, to samo drewno, te same obróbki.
-Tarasy i sauny to moje podwórko, nie oferta. Pokazuję je, żeby było widać, na czym stoi domek.
-Teraz projektuję domki dla innych. Jestem pierwszym klientem.</t>
+          <t>Zaczęło się od sauny. Wyszła dobrze, więc wziąłem się za altanę, no i ona też się udała.
+Domek był ostatni. Poszło w niego wszystko, czego nauczyły mnie tamte dwie budowy. Dlatego wyszedł najlepiej.
+I z całej trójki to jego budowałem najchętniej. Bo przy domku myśli się inaczej — nie o tym, jak ma wyglądać, tylko o tym, jak będą się w nim bawić dzieci. Żeby był wygodny, żeby wytrzymał i żeby nie trzeba było za niego przepłacać.
+Dziś wiem, że mam dość doświadczenia, żeby budować domki dla innych. I chcę budować właśnie je — nie dlatego, że to prostsze czy bardziej opłacalne, ale dlatego, że nic nie daje takiej satysfakcji, jak widok dziecka bawiącego się w czymś, co zrobiłem sam.</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -616,8 +616,10 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Zwykle trzeba wybrać: albo tanio, albo ładnie, albo na lata. Budowałem dla córek, więc nie wybierałem.
-2 × 3,6 m. Grafit i modrzew — ten sam, co na domu. Poziome elementy zakryte obróbkami blacharskimi, schody schowane pod konstrukcją. Nic nie gnije.</t>
+          <t>Zaczęło się od tego, że córka gdzieś zobaczyła domek i powiedziała, że też chce taki.
+Zanim usiadłem do projektu, obejrzałem, co jest na rynku. Większość domków buduje się tak, żeby wytrzymały jakieś pięć lat — potem dzieci wyrosną i można je spalić. Do tego wyglądają jak z bajki, a ja chciałem, żeby pasował do domu i do ogrodu. A te zrobione porządnie kosztowały ponad 20 tysięcy.
+Więc zbudowałem go sam. 2 × 3,6 m, materiały ze zwykłego składu — tylko poskładane porządnie. Poziome elementy zakryte obróbkami blacharskimi, schody schowane pod konstrukcją, żeby nic nie gniło. Projektowałem go razem z córką: ona mówiła, czego chce, ja patrzyłem, czy da się to zbudować.
+Chodziło o to, żeby w ogrodzie było wreszcie miejsce dla dzieci — żebym mógł spokojnie wypić kawę, kiedy bawią się same. Wyszło lepiej, niż zakładałem: domek stał się centrum ogrodu. To przy nim robimy urodziny i przesiadujemy letnie wieczory — już nie tylko dzieci.</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">

--- a/Instagram/PAVLOV_content_plan.xlsx
+++ b/Instagram/PAVLOV_content_plan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="510" yWindow="1060" windowWidth="25090" windowHeight="13730" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Лента" sheetId="1" state="visible" r:id="rId1"/>
@@ -70,7 +70,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5E3D3"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -101,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -115,18 +116,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -547,31 +552,31 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="151.2" customHeight="1">
-      <c r="A2" s="2" t="n">
+    <row r="2" ht="151.25" customFormat="1" customHeight="1" s="10">
+      <c r="A2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>KARUZELA</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>Запуск · день 1 · 📌 закрепить</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>Кто и откуда. Происхождение бренда и диапазон в одном посте</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>Двор целиком, где домик, терраса и сауна видны вместе — первый и главный кадр. Затем каждый объект отдельно: домик днём, терраса вечером, сауна на закате. 5–6 кадров</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>Zaczęło się od sauny. Wyszła dobrze, więc wziąłem się za altanę, no i ona też się udała.
 Domek był ostatni. Poszło w niego wszystko, czego nauczyły mnie tamte dwie budowy. Dlatego wyszedł najlepiej.
@@ -579,42 +584,42 @@
 Dziś wiem, że mam dość doświadczenia, żeby budować domki dla innych. I chcę budować właśnie je — nie dlatego, że to prostsze czy bardziej opłacalne, ale dlatego, że nic nie daje takiej satysfakcji, jak widok dziecka bawiącego się w czymś, co zrobiłem sam.</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>Последний кадр: «Wszystko, co pokazuję, stoi u mnie w ogrodzie.»</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="75.59999999999999" customHeight="1">
-      <c r="A3" s="2" t="n">
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="75.65000000000001" customFormat="1" customHeight="1" s="10">
+      <c r="A3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>KARUZELA</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>Запуск · день 1 · 📌 закрепить</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>Главный кейс. Как он сделан: конструктив, материалы, узлы</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>Домик снаружи: общий дневной, вид от дома, узел крупно, доборники на горизонталях, вечерний со светом. 6 кадров. Детей и игру НЕ брать — это отдельный пост</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>Zaczęło się od tego, że córka gdzieś zobaczyła domek i powiedziała, że też chce taki.
 Zanim usiadłem do projektu, obejrzałem, co jest na rynku. Większość domków buduje się tak, żeby wytrzymały jakieś pięć lat — potem dzieci wyrosną i można je spalić. Do tego wyglądają jak z bajki, a ja chciałem, żeby pasował do domu i do ogrodu. A te zrobione porządnie kosztowały ponad 20 tysięcy.
@@ -622,24 +627,24 @@
 Chodziło o to, żeby w ogrodzie było wreszcie miejsce dla dzieci — żebym mógł spokojnie wypić kawę, kiedy bawią się same. Wyszło lepiej, niż zakładałem: domek stał się centrum ogrodu. To przy nim robimy urodziny i przesiadujemy letnie wieczory — już nie tylko dzieci.</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>Последний кадр: «Domek można kupić. Własne miejsce — nie.»</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="75.59999999999999" customHeight="1">
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="75.65000000000001" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>KARUZELA</t>
+          <t>REELS</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -654,24 +659,25 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Дети в домике: разное время суток, разные занятия — играют, рисуют за столиком, прячутся, вечер со светом. Снимать по ходу, накопительно. 6–8 кадров. Лица по возможности не в кадре</t>
+          <t>Готовый смонтированный рилс: дети, собака и кот в домике, замедленная съёмка под весёлую музыку. Снимать заново не нужно.</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>СЦЕНЫ ЗАМЕНИ НА НАСТОЯЩИЕ — я их не знаю:
-Rano zabierają tam śniadanie, po południu rysują przy stoliku, wieczorem trzeba je stamtąd wyciągać.
-Dlatego w środku są firanki, półki i światło, a nie same ściany.</t>
+          <t>На экране в начале: «U nas jest tak»
+Подпись:
+Nie planowałem tego tak. Chciałem po prostu, żeby miały gdzie się bawić.
+A wyszło, że najwięcej z tego mam ja. One będą pamiętać domek. Ja będę pamiętać te wieczory.</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Последний кадр: «Dzieci wchodzą i zostają.»</t>
+          <t>Финальный экран: «U Was też tak może być.»</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -696,10 +702,299 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Эскиз оживает: линии прорисовываются, разворот проекта, ключевые детали крупно. Финал — размеры и вилка цены. 15–20 сек. Единый монтаж для всех эскизов</t>
+          <t>РИЛС по первому проекту. 6 слайдов из 9 рендеров и 2 планов.
+1 общий вид, терраса и домик вместе · 2 фасад, детали, узлы · 3 красивые кадры и план ·
+4 рендеры с сауной и план трансформации · 5 общий вид в контексте участка · 6 финальный кадр.
+Текст на кадре тремя блоками: средний · КРУПНЫЙ · мелкий курсивом.
+Тот же ролик идёт в кружок PROJEKTY отдельной заливкой в сторис.</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>НА ЭКРАНЕ, по слайдам:
+1. Wieczór, w którym nie trzeba wybierać
+RAZEM, NIE OSOBNO
+Miejsce, gdzie rozmowa przy stole i gra w domku dzieją się jednocześnie — kilka metrów od siebie.
+2. Nowoczesna bryła, grafit i drewno
+ZROBIONY JAK DOM
+Rynny, obróbki blacharskie i okucia prosto z budownictwa — żeby stał latami, a nie sezonami.
+3. To projekt koncepcyjny
+POD WASZĄ DZIAŁKĘ
+Przed budową siadamy razem: wymiary, materiały, zestaw zabaw. Każdy projekt dopasowuję do miejsca i do dziecka.
+4. Dzieci wyrosną, domek zostanie
+DRUGIE ŻYCIE
+Konstrukcja policzona tak, żeby wnętrze dało się zabudować: na dole sauna przy tarasie, na górze schowek albo pokój.
+5. Gdzie to się sprawdzi
+DOM ALBO HOTEL
+Przy nowoczesnym domu z większą działką, w hotelu, w każdym miejscu, gdzie dorośli i dzieci spędzają czas razem.
+6. Pełne wyposażenie, jak na wizualizacjach
+63 037 ZŁ
+Cały rozkład kosztów w opisie pod filmem.
+=== ОПИСАНИЕ ПОД РИЛСОМ ===
+To nie jest tylko domek dla dzieci. To pełnoprawna strefa wypoczynku połączona ze strefą zabaw — miejsce, które zostanie z Wami, kiedy dzieci dorosną, i będzie ozdobą działki przez lata.
+Przy zwykłym placu zabaw stoi się nad dzieckiem. Tutaj siedzicie na tarasie, a dzieci bawią się obok, w zasięgu wzroku. Przyjdą znajomi z dziećmi — dorośli zostają przy stole, dzieci mają swoje miejsce kilka metrów dalej.
+A kiedy wyrosną, zostaje gotowa strefa wypoczynku: sauna, taras, huśtawki, zieleń.
+Poniżej pełny skład — materiały i praca.
+MATERIAŁY — 27 037 zł
+Drewno — 12 760
+· Konstrukcja, sucha belka świerkowa 2,4 m³ — 5 280
+· Deska tarasowa kompozytowa 24 m² — 3 360
+· Deska modrzewiowa 15 m² — 1 350
+· Boazeria świerkowa 37 m² — 2 220
+· Sklejka 3 m² — 550
+Malowanie — 640
+· Impregnat grafitowy 15 l — 240
+· Olej do drewna 10 l — 400
+Pokrycie — 2 670
+· Gont 37 m² — 1 070
+· Poliwęglan komorowy 10 m² — 1 000
+· Akcesoria do poliwęglanu — 600
+Obróbki blacharskie — 1 897
+· Rynna 9 m — 270
+· Rura spustowa 12 m — 360
+· Akcesoria rynnowe — 400
+· Kątownik 42 m — 441
+· Gąsior 7 m — 132
+· Kątownik podrynnowy 9 m — 105
+· Zakończenia belek 18 m — 189
+Wyposażenie — 8 270
+· Sofa i stół — 2 400
+· Roleta rzymska z mocowaniem 2,3 × 5 m — 2 000
+· Zjeżdżalnia — 1 000
+· Drzwi — 600
+· Piasek 0,7 m³ — 420
+· Mocowania żaluzji — 400
+· Łączniki krzyżowe do lin 16 mm, 130 szt. — 390
+· Huśtawka talerzowa — 250
+· Chwyty wspinaczkowe 20 szt. — 240
+· Lina 60 m — 240
+· Pręty drewniane 20 mb — 200
+· Lina 5 m — 80
+· Huśtawka mała — 50
+Drobnica — 800
+· Wkręty, gwoździe, zszywki, łączniki
+PRACA — 36 000 zł
+· Adaptacja projektu i dokumentacja — 40 h
+· Produkcja — 280 h
+· Przygotowanie terenu i montaż — 40 h
+· Transport do 150 km — w cenie
+360 godzin × 100 zł
+RAZEM — 63 037 zł
+Ceny materiałów orientacyjne — z Allegro i od lokalnych dostawców. Wyposażenie pełne, dokładnie takie jak na wizualizacjach. Bez sauny i bez przebudowy, o której mówię na końcu.
+Projekt sprawdzi się przy nowoczesnym domu z większą działką, w hotelu albo w innym miejscu, gdzie dorośli i dzieci spędzają czas razem.</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Финальный экран: «Ten projekt szuka gospodarza.»</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="88.25" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>REELS</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Запуск · день 2</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Главный дифференциатор в движении. То, чего у конкурента физически нет</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Заход внутрь домика от первого лица, панорама по деталям: шторки, полки, книжки, столик, свет. Финал — вечерний кадр со светом. 15–20 сек</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>На экране:
+1) «Domek zwykle kupuje się pusty»
+2) «Firanki, półki, książki, światło»
+3) «U mnie to jeden komplet»
+4) «Nic do dokupienia»</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Финальный экран: «Napisz — powiem, co wchodzi w komplet.»</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="75.65000000000001" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>REELS</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Запуск · день 2</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Экспертиза и сохраняемость. Ловит человека до того, как он закажет у другого</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Кадр снизу под домиком, крупный план узла, доборники на горизонталях. Для контраста — как выглядит наружная лестница через пару лет, без указания на чужой объект. 20 сек</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>На экране:
+1) «W większości domków schody dostawia się z zewnątrz»
+2) «Po kilku sezonach są do wymiany»
+3) «Tutaj są pod konstrukcją, w suchym miejscu»</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Финальный экран: «Planujesz domek? Napisz przed zamówieniem — powiem, na co patrzeć.»</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="63" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>REELS</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Запуск · день 3 · 📌 закрепить</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Самый острый аргумент. Почему обычный домик портит участок, а этот — нет</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Два кадра типовых домиков — пластик, розовый, бревно. Из объявлений или стока, БЕЗ названий фирм. Затем свой на фоне дома, крупно совпадение графита домика с графитом дома. 15 сек</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>На экране:
+1) «Twój dom»
+2) «I to, co zwykle stawia się obok»
+3) «Domek może pasować do domu»
+4) «Ten sam grafit, to samo drewno»</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Финальный экран: «Napisz — dopasuję projekt do Twojego domu.»</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="75.65000000000001" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>REELS</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Запуск · день 3</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Объяснить цену, не называя процентов. Один человек против цепочки из шести</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>По кадру на роль: эскиз, каркас, доборники, электрика, посадка зелени, обстановка внутри. Финал — готовый домик целиком. 20 сек</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>На экране:
+1) «Żeby powstał taki domek, potrzeba sześciu osób»
+2) «Projektant, cieśla, blacharz, elektryk, ogrodnik, dekorator»
+3) «Sześć terminów, sześć marż»
+4) «Jeden wykonawca. Bez pośredników»</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Финальный экран: «Napisz — policzę pod Twoją działkę.»</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>REELS</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Запуск · день 3</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Второй проект. Другой размер и другой замысел, а не другая отделка</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Эскиз оживает: линии прорисовываются, разворот проекта, ключевые детали крупно. Финал — размеры и вилка цены. 15–20 сек. Единый монтаж для всех эскизов. Второй проект обязан отличаться от первого замыслом: другой размер, другая крыша, другой сценарий игры</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>ШАБЛОН, цифры твои. На экране:
 1) «Ten projekt szuka gospodarza» — хук, первые 2 секунды
@@ -709,238 +1004,18 @@
 5) «Zbuduję go raz — u Ciebie»</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Финальный экран: «Napisz — dopasuję go do Twojej działki.»</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Финальный экран: «Napisz — powiem, czy zmieści się u Ciebie.»</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="88.2" customHeight="1">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>REELS</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Запуск · день 2</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Главный дифференциатор в движении. То, чего у конкурента физически нет</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Заход внутрь домика от первого лица, панорама по деталям: шторки, полки, книжки, столик, свет. Финал — вечерний кадр со светом. 15–20 сек</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>На экране:
-1) «Domek zwykle kupuje się pusty»
-2) «Firanki, półki, książki, światło»
-3) «U mnie to jeden komplet»
-4) «Nic do dokupienia»</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Финальный экран: «Napisz — powiem, co wchodzi w komplet.»</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="75.59999999999999" customHeight="1">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>REELS</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Запуск · день 2</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Экспертиза и сохраняемость. Ловит человека до того, как он закажет у другого</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Кадр снизу под домиком, крупный план узла, доборники на горизонталях. Для контраста — как выглядит наружная лестница через пару лет, без указания на чужой объект. 20 сек</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>На экране:
-1) «W większości domków schody dostawia się z zewnątrz»
-2) «Po kilku sezonach są do wymiany»
-3) «Tutaj są pod konstrukcją, w suchym miejscu»</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Финальный экран: «Planujesz domek? Napisz przed zamówieniem — powiem, na co patrzeć.»</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="63" customHeight="1">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>REELS</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Запуск · день 3 · 📌 закрепить</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Самый острый аргумент. Почему обычный домик портит участок, а этот — нет</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Два кадра типовых домиков — пластик, розовый, бревно. Из объявлений или стока, БЕЗ названий фирм. Затем свой на фоне дома, крупно совпадение графита домика с графитом дома. 15 сек</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>На экране:
-1) «Twój dom»
-2) «I to, co zwykle stawia się obok»
-3) «Domek może pasować do domu»
-4) «Ten sam grafit, to samo drewno»</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Финальный экран: «Napisz — dopasuję projekt do Twojego domu.»</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="75.59999999999999" customHeight="1">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>REELS</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Запуск · день 3</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Объяснить цену, не называя процентов. Один человек против цепочки из шести</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>По кадру на роль: эскиз, каркас, доборники, электрика, посадка зелени, обстановка внутри. Финал — готовый домик целиком. 20 сек</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>На экране:
-1) «Żeby powstał taki domek, potrzeba sześciu osób»
-2) «Projektant, cieśla, blacharz, elektryk, ogrodnik, dekorator»
-3) «Sześć terminów, sześć marż»
-4) «Jeden wykonawca. Bez pośredników»</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>Финальный экран: «Napisz — policzę pod Twoją działkę.»</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>REELS</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Запуск · день 3</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Второй проект. Другой размер и другой замысел, а не другая отделка</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Эскиз оживает: линии прорисовываются, разворот проекта, ключевые детали крупно. Финал — размеры и вилка цены. 15–20 сек. Единый монтаж для всех эскизов. Второй проект обязан отличаться от первого замыслом: другой размер, другая крыша, другой сценарий игры</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>ШАБЛОН, цифры твои. На экране:
-1) «Ten projekt szuka gospodarza» — хук, первые 2 секунды
-2) «[Nazwa] — [wymiary]»
-3) «[Co w środku: konstrukcja, wyposażenie, światło]»
-4) «od [kwota] do [kwota]»
-5) «Zbuduję go raz — u Ciebie»</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>Финальный экран: «Napisz — powiem, czy zmieści się u Ciebie.»</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="75.59999999999999" customHeight="1">
+    <row r="11" ht="75.65000000000001" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
@@ -1141,7 +1216,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -1189,7 +1264,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="214.2" customHeight="1">
+    <row r="2" ht="214.25" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -1247,12 +1322,20 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>По карточке на эскиз: картинка, размеры, вилка цены. Единый шаблон, чтобы полка читалась полкой. Накопительный — каждый новый эскиз падает сюда</t>
+          <t>Первая карточка — правило, дальше по карточке на проект.
+Проект Domek_1 кладётся сюда тем же роликом, что идёт в ленту (позиция 4):
+залить видео отдельно в сторис, чтобы оно играло внутри кружка и не уводило в ленту.
+Накопительный — каждый новый эскиз падает сюда.</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Короткая подпись: название, размеры, вилка. Описания живут в посте, здесь только выбор</t>
+          <t>1. карточка-правило
+Każdy projekt buduję raz
+BEZ KOPII
+Ten domek stanie tylko u Was. Nie powtórzę go u nikogo innego — nawet jeśli ktoś poprosi.
+2. Domek_1 — ролик из позиции 4 «Ленты», тексты там же.
+Цена на финальном кадре: 63 037 zł, полная комплектация как на визуализациях.</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -1282,12 +1365,49 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Этапы стройки из того, что есть. На старте хватит пары сторис, наполнится на первой клиентской стройке</t>
+          <t>9 кадров, фото и короткие видео. Текст прямо на кадре, три блока:
+средний (до 5 слов) · КРУПНЫЙ (1–3 слова) · мелкий курсивом.
+Порядок = порядок публикации. Выкладывать от первого к девятому.</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Короткие подписи по этапам: что делается и зачем</t>
+          <t>1. модель в 3ds Max
+Zanim kupię pierwszą deskę
+PROJEKT 3D
+Cały domek powstaje najpierw w komputerze. Wiadomo, jak będzie wyglądał i ile kosztuje.
+2. куча стружки, дети с пакетами
+Cięcie i przygotowanie szkieletu
+U MNIE
+Góra wiórów zostaje w mojej pracowni, nie na Waszej działce.
+3. первая рама, дети рядом
+Domek składa się z ram
+RAMA PO RAMIE
+Każda powstaje osobno i w całości. Dopiero gotowe jadą na miejsce.
+4. окрашенные рамы
+Malowanie też wcześniej
+GOTOWE
+Na działkę przyjeżdża pomalowane. Żadnych puszek z farbą w trawie.
+5. разметка и бетонные блоки
+Konstrukcja stoi własnym ciężarem
+BEZ FUNDAMENTU
+Bloczki tylko wyrównują poziom. Nic nie trzeba wylewać ani kuć.
+6. каркас целиком
+Szkielet składa się w dwie godziny
+JAK KONTENER
+Ramy spięte razem dają sztywną, monolityczną bryłę. Dopiero na niej pojawiają się ściany, podłoga i dach.
+7. сверление декора, дочь с болтиками
+Po konstrukcji zaczyna się reszta
+DETALE
+Tego się nie przyspieszy. I to one robią różnicę.
+8. скриншот Allegro с мелочёвкой
+Firanki, lampki, drobiazgi
+W CENIE
+Dekor i wyposażenie wliczam w projekt. Nie ma listy rzeczy do dokupienia po odbiorze.
+9. финальный кадр
+Od projektu po ostatnią śrubę
+WSZYSTKO SAM
+Buduję sam i pokazuję każdy etap.</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -1297,7 +1417,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1456,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="75.59999999999999" customHeight="1">
+    <row r="6" ht="75.65000000000001" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -1352,24 +1472,44 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Фото себя за работой + карточки с текстом</t>
+          <t>ВИДЕО от первого лица, 7 кусков по 10–20 сек. Не карточки.
+Нумерация = порядок показа. Добавлять в кружок строго в этом порядке.
+Локации: 1 дома · 2 двор общим планом · 3 у домика · 4 с материалом или у верстака · 5 у домика · 6 где угодно · 7 финал.
+Вертикально, лицо в кадре с первой секунды, стикер «Субтитры» обязательно.
+Короткая надпись — в ВЕРХНЕЙ трети кадра: внизу субтитры и интерфейс Instagram.
+Куски независимы: можно переснимать по одному и снимать в разные дни.
+Текст не читать с листа — выучить и говорить своими словами.</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Jestem pierwszym klientem.
-Chciałem, żeby córki miały swoje miejsce, a nie plastikowy zamek z marketu. Na rynku takiego nie było — więc zrobiłem sam.
-Teraz projektuję domki dla innych.</t>
+          <t>1. НА ЭКРАНЕ: Kto to robi i dlaczego.
+Cześć, jestem Alex. Z szacunku do Waszego czasu — krótko: co robię i dlaczego.
+2. НА ЭКРАНЕ: Trzy lata. Sauna, altana, domek.
+Jesteśmy tu z rodziną od trzech lat. I przez ten czas udało mi się wybudować saunę, altanę i ten domek.
+3. НА ЭКРАНЕ: Projekt, budowa i firanki — jedna osoba.
+Jestem architektem, ale mam też ręce. Projektuję, buduję — wszystko, aż po firanki na Allegro.
+Dlatego nie chcę powtarzać tego samego domku — wolę zrobić coś pod konkretne dziecko i konkretny ogród.
+4. НА ЭКРАНЕ: Domek, który pasuje do Twojego ogrodu.
+W Polsce jest dużo dobrych producentów. Jedni budują tanio i szybko, inni robią bardzo drogie place zabaw dla przedszkoli i galerii handlowych. Ja chcę zaproponować coś pomiędzy: jakość i styl za pieniądze, które mają sens.
+5. НА ЭКРАНЕ: „Wolałabym, żeby to była twoja praca."
+Kiedy rysowałem ten domek, córka zapytała, czy pracuję. Powiedziałem, że nie — że robię to dla nich.
+Popatrzyła chwilę i mówi: „Wolałabym, żeby to była twoja praca."
+No i pomyślałem, że warto spróbować.
+6. НА ЭКРАНЕ: Nie muszę tego robić. Robię, bo chcę.
+Mam pracę, która nas utrzymuje. A to buduję dlatego, że wychodzi mi nieźle i chcę robić coś swojego. Pieniądze też się przydadzą — ale nie od nich zaczynam.
+7. НА ЭКРАНЕ: Dzieci rosną szybciej, niż się wydaje.
+Na koniec powiem jeszcze jedno. Łatwo przegapić te kilka lat, kiedy jesteśmy dzieciom naprawdę potrzebni. Siedząc w pracy, gonimy za czymś, a one w tym czasie zdążą urosnąć. Więc póki są małe, warto spędzać z nimi jak najwięcej czasu — a ja chętnie pomogę Wam stworzyć miejsce, w którym będzie się chciało ten czas spędzać.</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>«Zaczynam od siebie. Dosłownie.»</t>
+          <t>«...a ja chętnie pomogę Wam stworzyć miejsce, w którym będzie się chciało ten czas spędzać.»</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1439,360 +1579,360 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Лента</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Карусели и рилсы. Сначала девять позиций запуска, ниже — то, что идёт дальше по ритму</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Сторис</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Кружки и живые сторис. Один кружок — одна строка, карточки внутри ячейки</t>
         </is>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Цель</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Зачем эта публикация. Если цель не формулируется — публикации нет. Наполнения ради наполнения в таблице не держим</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>КОЛОНКИ</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Сценарий: кадры по порядку, количество, откуда снимать</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Цель</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Зачем эта публикация. Если цель не формулируется — публикации нет</t>
         </is>
       </c>
     </row>
     <row r="7" ht="50" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Что снимать</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Кадры по порядку, количество, откуда снимать</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Текст</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Для карусели — подпись под постом. Для рилса — текст на экране по кадрам, 85% смотрят без звука</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+    <row r="9" ht="25" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Концовка</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Каждая ведёт к контакту и называет, что человек получит за сообщение. Исключение — пост о происхождении: там концовка закрывает историю</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Статус</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>⬜ не снято · 🟡 снято, не опубликовано · ✅ опубликовано</t>
         </is>
       </c>
     </row>
     <row r="11" ht="25" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Модель</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Авторская. Я придумываю проекты, клиент выбирает из моих, дальше адаптация под участок и стройка. Не подрядчик, берущий чужую идею</t>
         </is>
       </c>
     </row>
     <row r="12" ht="25" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>ЯДРО</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Только детские домики. Терраса и сауна — портфолио, их никто не предлагает купить</t>
         </is>
       </c>
     </row>
     <row r="13" ht="25" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Модель</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Авторская. Проекты мои, клиент выбирает из моих, дальше адаптация под участок и стройка</t>
         </is>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Продукт</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Только детские домики. Терраса и сауна — своё подворье, не оферта</t>
         </is>
       </c>
     </row>
     <row r="15" ht="37.5" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Эскиз</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Главный источник публикаций: не упирается в то, что построено. Пока объект один, ленту держат эскизы</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+    <row r="16" ht="25" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Цена</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>На эскизе стоит ВИЛКА, не итог: проект с одними качелями и он же с двумя — разные деньги. Итог появляется после адаптации</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Уникальность</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>Каждый проект строится один раз. Копию не получит никто, включая копию твоего</t>
         </is>
       </c>
     </row>
     <row r="18" ht="25" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Пропорция</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>Рилсов больше, чем каруселей, и это правильно на старте: рилс — единственный холодный вход, карусель работает на тех, кто уже пришёл</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>PROJEKTY</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>Что можно заказать сейчас. Первая карточка — правило, дальше эскизы с ценами</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>ЗАПУСК</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Снять страх неизвестности. Четыре шага, больше ничего</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Предусловие</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>Не открывать, пока нет минимум двух эскизов. Узкое место не время, а количество проектов</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="22" ht="25" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Закрепить</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Три поста уходят наверх сетки и стоят там всегда: двор, домик и дизайн — кто, что построил, чем отличаюсь. Помечены 📌 в колонке «Куда»</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="23" ht="25" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Ритм сетки</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>Позиции в сетке не нумеруются: они живут до десятого поста, дальше всё сползает вниз. Постоянны только три закреплённых. Единственное правило очереди — два эскиза подряд не ставить</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="24" ht="25" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>День 1–3</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>День 1 — три карусели, чтобы в профиле было что смотреть. Дни 2 и 3 — рилсы: рилс гонит трафик в профиль, и профиль к этому моменту не должен быть пустым</t>
         </is>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Дальше</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>2 рилса + 1 карусель в неделю. Сторис через день. Ключевое — отсутствие провалов</t>
         </is>
       </c>
     </row>
     <row r="26" ht="25" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Нумерация</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>№1–9 — позиции в сетке при чтении, слева сверху. Публиковать в ОБРАТНОМ порядке: №9 первым, №1 последним</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>ВАЖНО</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>Позиции 1, 2 и 9: кто → что построил → что предлагает</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>Рилс остаётся навсегда</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Любой рилс попадает в сетку как обычный пост. Планка не ниже, чем для карусели</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Обложка</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>Для каждого рилса выбрать вручную, иначе превью возьмётся из середины и сломает сетку</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Метрика</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Сохранения и переходы в директ. Не лайки и не подписчики</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>Пока это правда</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>«Осталось 2 места» ставить, только пока мест действительно 2</t>
         </is>

--- a/Instagram/PAVLOV_content_plan.xlsx
+++ b/Instagram/PAVLOV_content_plan.xlsx
@@ -1280,19 +1280,27 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>4 карточки текстом на фоне эскизов и своих объектов. Ставятся один раз и дальше не меняются</t>
+          <t>Три сторис — по одной на продукт. Текст на кадре тремя блоками:
+средний (до 5 слов) · КРУПНЫЙ (1–3 слова) · мелкий курсивом.
+Фоны: 1 эскизы, 2 свои объекты, 3 чертежи и планы.
+Ставятся один раз и дальше не меняются.
+Вводная про «беру 2–3 проекта в полгода» снята: объявляется, когда пойдут запросы.</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>1) Na najbliższe pół roku przyjmuję 2–3 projekty. Tyle, ile mogę poprowadzić sam.
-   Każdy projekt powstaje raz — zbuduję go u Ciebie i nie powtórzę u nikogo.
-2) Jak to działa: wybierasz projekt → dopasowuję do Twojej działki, potrzeb i budżetu →
-   ustalamy zakres i kwotę, bez zmian po drodze → buduję i urządzam.
-3) Co wchodzi w cenę: materiały po cenie zakupu z paragonami · konstrukcja i obróbki ·
-   światło · firanki, półki, tekstylia · montaż.
-   Moja praca to kwota ustalona przed startem.
-4) Masz działkę i dzieci? Napisz — powiem, który projekt się zmieści.</t>
+          <t>1. готовые проекты
+Projekty z mojej półki
+GOTOWE DO ADAPTACJI
+W moich projektach znajdziecie połączenie strefy wypoczynku dla dorosłych z placem zabaw dla dzieci. Elementy zabawowe dobieram pojedynczo, pod konkretne dziecko. Całość dopasowuję do działki i budżetu.
+2. реализация на заказ
+Macie swój pomysł albo projekt
+ZBUDUJĘ TO
+Od pierwszej belki po firanki — wszystko robię sam, bez podwykonawców. Dopilnuję, żeby nic nie gniło i nie nasiąkało wodą, a obiekt trzymał wygląd przez lata.
+3. проектирование отдельно
+Budujecie sami albo ze swoją ekipą
+PROJEKT OSOBNO
+Koncepcja — 800 zł: rysunki i wizualizacje, po których widać, co powstanie. Pełna dokumentacja z węzłami, wymiarami i kosztorysem — 4 000 zł. Jeśli budowę prowadzę ja, koncepcję odliczam od ceny.</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -1302,7 +1310,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1353,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>

--- a/Instagram/PAVLOV_content_plan.xlsx
+++ b/Instagram/PAVLOV_content_plan.xlsx
@@ -1338,12 +1338,13 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>1. карточка-правило
-Każdy projekt buduję raz
-BEZ KOPII
-Ten domek stanie tylko u Was. Nie powtórzę go u nikogo innego — nawet jeśli ktoś poprosi.
-2. Domek_1 — ролик из позиции 4 «Ленты», тексты там же.
-Цена на финальном кадре: 63 037 zł, полная комплектация как на визуализациях.</t>
+          <t>1. Domek_1 — ОПУБЛИКОВАН. Ролик из позиции 4 «Ленты», тексты там же.
+Цена на финальном кадре: 63 037 zł, полная комплектация как на визуализациях.
+2. Карточка-правило — НЕ ставилась, можно добавить первой:
+Projekt jest jeden, realizacje różne
+POD WAS
+Ten sam projekt na innej działce, z innymi dziećmi i innym budżetem staje się czymś swoim. Dlatego dwa takie same nie powstaną.
+Старая редакция («Każdy projekt buduję raz / BEZ KOPII») снята: решение об однократной реализации отменено 5 октября, см. CONTEXT.md.</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">

--- a/Instagram/PAVLOV_content_plan.xlsx
+++ b/Instagram/PAVLOV_content_plan.xlsx
@@ -791,7 +791,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
